--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_10sep26_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_10sep26_Thurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BBDB6A-253A-4DDA-8BB1-B095AB3CB237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D51800D-468E-431E-91E6-079C343515E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="289">
   <si>
     <t>Date</t>
   </si>
@@ -902,6 +902,9 @@
   </si>
   <si>
     <t>S 250*225.5 :10 SEP 2026 10:59:02 AM</t>
+  </si>
+  <si>
+    <t>S 10*1548 :31 AUG 2026 11:12:50 AM</t>
   </si>
 </sst>
 </file>
@@ -1643,35 +1646,37 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>2560</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-22.299450629999999</v>
+        <v>1.3125512720000001</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="H2" s="5">
-        <v>3294.7</v>
+        <v>2438</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="41"/>
+      <c r="J2" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
@@ -1679,13 +1684,15 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B2, $C$2:$C$776, C2, $D$2:$D$776, D2, $E$2:$E$776, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>62</v>
+      <c r="O2" s="10"/>
+      <c r="P2" s="25"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -1694,21 +1701,21 @@
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>3914</v>
+        <v>13552</v>
       </c>
       <c r="F3" s="4">
-        <v>-21.985250149999999</v>
+        <v>1.0739856800000001</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H3" s="5">
-        <v>5017</v>
+        <v>13408</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="41" t="s">
         <v>41</v>
       </c>
       <c r="K3" s="17"/>
@@ -1718,36 +1725,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B3, $C$2:$C$776, C3, $D$2:$D$776, D3, $E$2:$E$776, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4">
-        <v>660</v>
+        <v>2435</v>
       </c>
       <c r="F4" s="4">
-        <v>-20.390808759999999</v>
+        <v>-0.1230516817</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="H4" s="5">
-        <v>829.05</v>
+        <v>2438</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="41"/>
+      <c r="J4" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
@@ -1755,36 +1766,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B4, $C$2:$C$776, C4, $D$2:$D$776, D4, $E$2:$E$776, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4">
-        <v>4014</v>
+        <v>2370</v>
       </c>
       <c r="F5" s="4">
-        <v>-19.992027109999999</v>
+        <v>-0.2105263158</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H5" s="5">
-        <v>5017</v>
+        <v>2375</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="41"/>
+      <c r="J5" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
@@ -1792,36 +1807,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B5, $C$2:$C$776, C5, $D$2:$D$776, D5, $E$2:$E$776, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>62</v>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
+        <v>46252.645138888889</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
-        <v>2660</v>
+        <v>401</v>
       </c>
       <c r="F6" s="4">
-        <v>-19.26427292</v>
+        <v>-0.49627791560000001</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5">
-        <v>3294.7</v>
+        <v>403</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="41"/>
+      <c r="J6" s="43" t="s">
+        <v>41</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
@@ -1829,142 +1848,177 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B6, $C$2:$C$776, C6, $D$2:$D$776, D6, $E$2:$E$776, E6) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>62</v>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
+        <v>46269.375</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E7" s="4">
-        <v>18052</v>
+        <v>348</v>
       </c>
       <c r="F7" s="4">
-        <v>-19.212351760000001</v>
+        <v>-0.79817559859999998</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5">
-        <v>22345</v>
+        <v>350.8</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="41"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
+      <c r="J7" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="L7" s="18">
+        <v>9000</v>
+      </c>
+      <c r="M7" s="27">
+        <f>ABS((D7*E7)-L7)</f>
+        <v>300</v>
+      </c>
       <c r="N7" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B7, $C$2:$C$776, C7, $D$2:$D$776, D7, $E$2:$E$776, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
-        <v>46252.688194444447</v>
+        <v>46275.457662037035</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E8" s="4">
-        <v>136.15</v>
+        <v>222</v>
       </c>
       <c r="F8" s="4">
-        <v>-17.424793789999999</v>
+        <v>-0.81758477419999998</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H8" s="5">
-        <v>164.88</v>
+        <v>223.83</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="41"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" t="str">
+      <c r="J8" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="L8" s="18">
+        <v>56375</v>
+      </c>
+      <c r="M8" s="18">
+        <f>ABS((D8*E8)-L8)</f>
+        <v>34175</v>
+      </c>
+      <c r="N8" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B8, $C$2:$C$776, C8, $D$2:$D$776, D8, $E$2:$E$776, E8) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>62</v>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4">
-        <v>4164</v>
+        <v>205</v>
       </c>
       <c r="F9" s="4">
-        <v>-17.00219255</v>
+        <v>-0.96618357489999995</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
-        <v>5017</v>
+        <v>207</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" t="str">
+      <c r="J9" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L9" s="18">
+        <v>10550</v>
+      </c>
+      <c r="M9" s="18">
+        <f>ABS((D9*E9)-L9)</f>
+        <v>300</v>
+      </c>
+      <c r="N9" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B9, $C$2:$C$776, C9, $D$2:$D$776, D9, $E$2:$E$776, E9) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" s="34" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+    </row>
+    <row r="10" spans="1:16" s="34" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E10" s="4">
-        <v>18552</v>
+        <v>3888</v>
       </c>
       <c r="F10" s="4">
-        <v>-16.9747147</v>
+        <v>-1.1944091489999999</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="H10" s="5">
-        <v>22345</v>
+        <v>3935</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
@@ -1977,75 +2031,88 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B10, $C$2:$C$776, C10, $D$2:$D$776, D10, $E$2:$E$776, E10) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O10"/>
-      <c r="P10"/>
-    </row>
-    <row r="11" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>62</v>
+      <c r="O10" s="26"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>46265.466666666667</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
-        <v>2752</v>
+        <v>1503</v>
       </c>
       <c r="F11" s="4">
-        <v>-16.47190943</v>
+        <v>-1.4426229509999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H11" s="5">
-        <v>3294.7</v>
+        <v>1525</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="41"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
+      <c r="J11" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="L11" s="18">
+        <v>15480</v>
+      </c>
+      <c r="M11" s="18">
+        <f>ABS((D11*E11)-L11)</f>
+        <v>450</v>
+      </c>
       <c r="N11" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B11, $C$2:$C$776, C11, $D$2:$D$776, D11, $E$2:$E$776, E11) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O11" s="10"/>
+      <c r="P11" s="25"/>
+    </row>
+    <row r="12" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E12" s="4">
-        <v>19052</v>
+        <v>281</v>
       </c>
       <c r="F12" s="4">
-        <v>-14.73707765</v>
+        <v>-1.662292213</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H12" s="5">
-        <v>22345</v>
+        <v>285.75</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="41"/>
+      <c r="J12" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
@@ -2053,36 +2120,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B12, $C$2:$C$776, C12, $D$2:$D$776, D12, $E$2:$E$776, E12) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
-        <v>62</v>
+      <c r="O12" s="10"/>
+      <c r="P12" s="26"/>
+    </row>
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E13" s="4">
-        <v>196</v>
+        <v>203.5</v>
       </c>
       <c r="F13" s="4">
-        <v>-13.27433628</v>
+        <v>-1.690821256</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H13" s="5">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="41"/>
+      <c r="J13" s="42" t="s">
+        <v>55</v>
+      </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
@@ -2090,38 +2161,37 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B13, $C$2:$C$776, C13, $D$2:$D$776, D13, $E$2:$E$776, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>4364</v>
+        <v>3856</v>
       </c>
       <c r="F14" s="4">
-        <v>-13.015746460000001</v>
+        <v>-2.0076238879999999</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="H14" s="5">
-        <v>5017</v>
+        <v>3935</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="42" t="s">
-        <v>41</v>
-      </c>
+      <c r="J14" s="41"/>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
@@ -2129,37 +2199,39 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B14, $C$2:$C$776, C14, $D$2:$D$776, D14, $E$2:$E$776, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O14" s="19"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E15" s="4">
-        <v>701</v>
+        <v>878</v>
       </c>
       <c r="F15" s="4">
-        <v>-12.609861</v>
+        <v>-2.1181716829999999</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="H15" s="5">
-        <v>802.15</v>
+        <v>897</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K15" s="17"/>
       <c r="L15" s="17"/>
@@ -2168,59 +2240,54 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B15, $C$2:$C$776, C15, $D$2:$D$776, D15, $E$2:$E$776, E15) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="29">
-        <v>46255</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="31">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31">
-        <v>19550</v>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+    </row>
+    <row r="16" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1132</v>
       </c>
       <c r="F16" s="4">
-        <v>-12.508391140000001</v>
+        <v>-2.1776702389999998</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H16" s="5">
-        <v>22345</v>
+        <v>1157.2</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J16" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="L16" s="27">
-        <v>19992</v>
-      </c>
-      <c r="M16" s="27">
-        <f>ABS((D16*E16)-L16)</f>
-        <v>442</v>
-      </c>
-      <c r="N16" s="28" t="str">
+      <c r="J16" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B16, $C$2:$C$776, C16, $D$2:$D$776, D16, $E$2:$E$776, E16) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="17" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
-        <v>46252.635416666664</v>
+        <v>46269.375</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
@@ -2229,95 +2296,118 @@
         <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>2892</v>
+        <v>3210</v>
       </c>
       <c r="F17" s="4">
-        <v>-12.222660640000001</v>
+        <v>-2.3692934700000001</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H17" s="5">
-        <v>3294.7</v>
+        <v>3287.9</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
+      <c r="J17" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="L17" s="18">
+        <v>6880</v>
+      </c>
+      <c r="M17" s="27">
+        <f>ABS((D17*E17)-L17)</f>
+        <v>460</v>
+      </c>
       <c r="N17" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B17, $C$2:$C$776, C17, $D$2:$D$776, D17, $E$2:$E$776, E17) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
-        <v>62</v>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>46260.375</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="4">
-        <v>4410</v>
+        <v>2348</v>
       </c>
       <c r="F18" s="4">
-        <v>-12.09886386</v>
+        <v>-2.5321710249999998</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H18" s="5">
-        <v>5017</v>
+        <v>2409</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="41"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
+      <c r="J18" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="L18" s="18">
+        <v>7344</v>
+      </c>
+      <c r="M18" s="18">
+        <f>ABS((D18*E18)-L18)</f>
+        <v>300</v>
+      </c>
       <c r="N18" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B18, $C$2:$C$776, C18, $D$2:$D$776, D18, $E$2:$E$776, E18) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>111</v>
+        <v>13052</v>
       </c>
       <c r="F19" s="4">
-        <v>-12.086171390000001</v>
+        <v>-2.6551312650000001</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H19" s="5">
-        <v>126.26</v>
+        <v>13408</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="41"/>
+      <c r="J19" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
@@ -2326,30 +2416,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="20" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>4415</v>
+        <v>3830</v>
       </c>
       <c r="F20" s="4">
-        <v>-10.29886832</v>
+        <v>-2.6683608639999998</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="H20" s="5">
-        <v>4921.8999999999996</v>
+        <v>3935</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
@@ -2362,157 +2452,177 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B20, $C$2:$C$776, C20, $D$2:$D$776, D20, $E$2:$E$776, E20) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="3">
-        <v>46267.375</v>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+    </row>
+    <row r="21" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>20050</v>
+        <v>4010</v>
       </c>
       <c r="F21" s="4">
-        <v>-10.27075408</v>
+        <v>-2.669902913</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5">
-        <v>22345</v>
+        <v>4120</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="L21" s="18">
-        <v>20350</v>
-      </c>
-      <c r="M21" s="18">
-        <f>ABS((D21*E21)-L21)</f>
-        <v>300</v>
-      </c>
-      <c r="N21" s="10" t="str">
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B21, $C$2:$C$776, C21, $D$2:$D$776, D21, $E$2:$E$776, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
-        <v>62</v>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="3">
+        <v>46274.375</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E22" s="4">
-        <v>251</v>
+        <v>1005</v>
       </c>
       <c r="F22" s="4">
-        <v>-10.228898429999999</v>
+        <v>-2.7199690250000002</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="H22" s="5">
-        <v>279.60000000000002</v>
+        <v>1033.0999999999999</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="41"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" t="str">
+      <c r="J22" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="L22" s="18">
+        <v>15600</v>
+      </c>
+      <c r="M22" s="18">
+        <f>ABS((D22*E22)-L22)</f>
+        <v>525</v>
+      </c>
+      <c r="N22" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B22, $C$2:$C$776, C22, $D$2:$D$776, D22, $E$2:$E$776, E22) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P22" s="34"/>
-    </row>
-    <row r="23" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>62</v>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E23" s="4">
-        <v>4456</v>
+        <v>1664</v>
       </c>
       <c r="F23" s="4">
-        <v>-9.465856681</v>
+        <v>-2.7469316190000002</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="H23" s="5">
-        <v>4921.8999999999996</v>
+        <v>1711</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J23" s="41"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" t="str">
+      <c r="J23" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="L23" s="18">
+        <f>5*1794</f>
+        <v>8970</v>
+      </c>
+      <c r="M23" s="18">
+        <f>ABS((D23*E23)-L23)</f>
+        <v>650</v>
+      </c>
+      <c r="N23" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B23, $C$2:$C$776, C23, $D$2:$D$776, D23, $E$2:$E$776, E23) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E24" s="4">
-        <v>115.25</v>
+        <v>201</v>
       </c>
       <c r="F24" s="4">
-        <v>-8.7201013780000007</v>
+        <v>-2.8985507250000002</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="H24" s="5">
-        <v>126.26</v>
+        <v>207</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="41"/>
+      <c r="J24" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
@@ -2521,35 +2631,37 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="25" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
-        <v>62</v>
+    <row r="25" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="4">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="E25" s="4">
-        <v>1751</v>
+        <v>391</v>
       </c>
       <c r="F25" s="4">
-        <v>-8.4205020919999995</v>
+        <v>-2.9776674939999999</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="H25" s="5">
-        <v>1912</v>
+        <v>403</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="41"/>
+      <c r="J25" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
@@ -2557,36 +2669,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B25, $C$2:$C$776, C25, $D$2:$D$776, D25, $E$2:$E$776, E25) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
-        <v>62</v>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+    </row>
+    <row r="26" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D26" s="4">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E26" s="4">
-        <v>116</v>
+        <v>277</v>
       </c>
       <c r="F26" s="4">
-        <v>-8.1260890230000005</v>
+        <v>-3.0621172350000001</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H26" s="5">
-        <v>126.26</v>
+        <v>285.75</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="41"/>
+      <c r="J26" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
@@ -2594,31 +2710,32 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B26, $C$2:$C$776, C26, $D$2:$D$776, D26, $E$2:$E$776, E26) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>62</v>
+      <c r="P26" s="10"/>
+    </row>
+    <row r="27" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D27" s="4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E27" s="4">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="F27" s="4">
-        <v>-7.9658669529999999</v>
+        <v>-3.0758226039999998</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="H27" s="5">
-        <v>223.83</v>
+        <v>279.60000000000002</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
@@ -2633,38 +2750,38 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B27, $C$2:$C$776, C27, $D$2:$D$776, D27, $E$2:$E$776, E27) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D28" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E28" s="4">
-        <v>836</v>
+        <v>3810</v>
       </c>
       <c r="F28" s="4">
-        <v>-7.9295154190000003</v>
+        <v>-3.1766200759999998</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="H28" s="5">
-        <v>908</v>
+        <v>3935</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="41" t="s">
-        <v>118</v>
-      </c>
+      <c r="J28" s="41"/>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
@@ -2672,13 +2789,15 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B28, $C$2:$C$776, C28, $D$2:$D$776, D28, $E$2:$E$776, E28) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
-        <v>62</v>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
@@ -2687,16 +2806,16 @@
         <v>5</v>
       </c>
       <c r="E29" s="4">
-        <v>1614</v>
+        <v>1142</v>
       </c>
       <c r="F29" s="4">
-        <v>-7.8241005140000004</v>
+        <v>-3.220338983</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H29" s="5">
-        <v>1751</v>
+        <v>1180</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
@@ -2711,36 +2830,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B29, $C$2:$C$776, C29, $D$2:$D$776, D29, $E$2:$E$776, E29) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+    </row>
+    <row r="30" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
-        <v>46252.635416666664</v>
+        <v>46252.6875</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D30" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E30" s="4">
-        <v>1410</v>
+        <v>122</v>
       </c>
       <c r="F30" s="4">
-        <v>-7.5409836070000003</v>
+        <v>-3.3739901790000002</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H30" s="5">
-        <v>1525</v>
+        <v>126.26</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="41"/>
+      <c r="J30" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
@@ -2748,121 +2871,119 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B30, $C$2:$C$776, C30, $D$2:$D$776, D30, $E$2:$E$776, E30) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="3">
-        <v>46254.375</v>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+    </row>
+    <row r="31" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D31" s="4">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="E31" s="4">
-        <v>2230</v>
+        <v>31.01</v>
       </c>
       <c r="F31" s="4">
-        <v>-7.4304690740000003</v>
+        <v>-3.5158680769999999</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H31" s="5">
-        <v>2409</v>
+        <v>32.14</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J31" s="23" t="s">
+      <c r="J31" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="K31" s="17" t="s">
-        <v>148</v>
-      </c>
+      <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
-      <c r="N31" s="10" t="str">
+      <c r="N31" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B31, $C$2:$C$776, C31, $D$2:$D$776, D31, $E$2:$E$776, E31) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="3">
-        <v>46031.4375</v>
+      <c r="O31" s="34"/>
+    </row>
+    <row r="32" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>216</v>
+        <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="4">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="E32" s="4">
-        <v>1052</v>
+        <v>862</v>
       </c>
       <c r="F32" s="4">
-        <v>-7.3902900660000004</v>
+        <v>-3.9018952059999998</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>227</v>
+        <v>52</v>
       </c>
       <c r="H32" s="5">
-        <v>1135.95</v>
+        <v>897</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="24" t="s">
+      <c r="J32" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="18"/>
-      <c r="L32" s="18"/>
-      <c r="M32" s="18">
-        <f>ABS((D32*E32)-L32)</f>
-        <v>3156</v>
-      </c>
-      <c r="N32" s="10" t="str">
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
+      <c r="N32" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B32, $C$2:$C$776, C32, $D$2:$D$776, D32, $E$2:$E$776, E32) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O32" s="10"/>
-      <c r="P32" s="19"/>
-    </row>
-    <row r="33" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
-        <v>62</v>
+    </row>
+    <row r="33" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D33" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33" s="4">
-        <v>4560</v>
+        <v>640</v>
       </c>
       <c r="F33" s="4">
-        <v>-7.3528515409999997</v>
+        <v>-3.9039039039999999</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="H33" s="5">
-        <v>4921.8999999999996</v>
+        <v>666</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="41"/>
+      <c r="J33" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K33" s="17"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
@@ -2871,30 +2992,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="34" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
-        <v>46252.6875</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E34" s="4">
-        <v>326</v>
+        <v>1302</v>
       </c>
       <c r="F34" s="4">
-        <v>-7.0695553020000004</v>
+        <v>-3.9114391140000002</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H34" s="5">
-        <v>350.8</v>
+        <v>1355</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>8</v>
@@ -2910,12 +3031,12 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="35" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="6" t="s">
-        <v>62</v>
+    <row r="35" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="3">
+        <v>46258.375694444447</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
@@ -2924,60 +3045,71 @@
         <v>10</v>
       </c>
       <c r="E35" s="4">
-        <v>561</v>
+        <v>1465</v>
       </c>
       <c r="F35" s="4">
-        <v>-6.9111424540000002</v>
+        <v>-3.9344262300000001</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H35" s="5">
-        <v>602.65</v>
+        <v>1525</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" t="str">
+      <c r="J35" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="L35" s="18">
+        <v>15100</v>
+      </c>
+      <c r="M35" s="18">
+        <f>ABS((D35*E35)-L35)</f>
+        <v>450</v>
+      </c>
+      <c r="N35" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B35, $C$2:$C$776, C35, $D$2:$D$776, D35, $E$2:$E$776, E35) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+    </row>
+    <row r="36" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>46252.635416666664</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D36" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E36" s="4">
-        <v>1420</v>
+        <v>1132</v>
       </c>
       <c r="F36" s="4">
-        <v>-6.8852459020000003</v>
+        <v>-4.0677966100000003</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H36" s="5">
-        <v>1525</v>
+        <v>1180</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="41"/>
+      <c r="J36" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
@@ -2985,10 +3117,12 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B36, $C$2:$C$776, C36, $D$2:$D$776, D36, $E$2:$E$776, E36) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+    </row>
+    <row r="37" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
-        <v>46252.635416666664</v>
+        <v>46268.375</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>32</v>
@@ -2997,13 +3131,13 @@
         <v>10</v>
       </c>
       <c r="D37" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E37" s="4">
-        <v>850</v>
+        <v>870.2</v>
       </c>
       <c r="F37" s="4">
-        <v>-6.3876651979999997</v>
+        <v>-4.1629955949999999</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>85</v>
@@ -3014,155 +3148,192 @@
       <c r="I37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J37" s="42" t="s">
+      <c r="J37" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" t="str">
+      <c r="K37" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="L37" s="18">
+        <v>17920</v>
+      </c>
+      <c r="M37" s="18">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>516</v>
+      </c>
+      <c r="N37" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B37, $C$2:$C$776, C37, $D$2:$D$776, D37, $E$2:$E$776, E37) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O37" s="10"/>
-    </row>
-    <row r="38" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="6" t="s">
-        <v>62</v>
+      <c r="P37" s="10"/>
+    </row>
+    <row r="38" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E38" s="4">
-        <v>411</v>
+        <v>870</v>
       </c>
       <c r="F38" s="4">
-        <v>-6.3354603459999996</v>
+        <v>-4.1850220260000004</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="H38" s="5">
-        <v>438.8</v>
+        <v>908</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="41"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" t="str">
+      <c r="J38" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="L38" s="18">
+        <v>17700</v>
+      </c>
+      <c r="M38" s="18">
+        <f>ABS((D38*E38)-L38)</f>
+        <v>300</v>
+      </c>
+      <c r="N38" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B38, $C$2:$C$776, C38, $D$2:$D$776, D38, $E$2:$E$776, E38) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>62</v>
+      <c r="O38" s="10"/>
+      <c r="P38" s="25"/>
+    </row>
+    <row r="39" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="20">
+        <v>46255</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4">
-        <v>4710</v>
+        <v>336</v>
       </c>
       <c r="F39" s="4">
-        <v>-6.119194738</v>
+        <v>-4.2189281640000003</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="H39" s="5">
-        <v>5017</v>
+        <v>350.8</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="41" t="s">
+      <c r="J39" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" t="str">
+      <c r="K39" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="L39" s="18">
+        <v>8700</v>
+      </c>
+      <c r="M39" s="18">
+        <f>ABS((D39*E39)-L39)</f>
+        <v>300</v>
+      </c>
+      <c r="N39" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B39, $C$2:$C$776, C39, $D$2:$D$776, D39, $E$2:$E$776, E39) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="40" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>62</v>
+    <row r="40" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D40" s="4">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="E40" s="4">
-        <v>1277</v>
+        <v>214</v>
       </c>
       <c r="F40" s="4">
-        <v>-5.7564575649999998</v>
+        <v>-4.3917258629999996</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="H40" s="5">
-        <v>1355</v>
+        <v>223.83</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="41"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" t="str">
+      <c r="J40" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="L40" s="18">
+        <v>21900</v>
+      </c>
+      <c r="M40" s="18">
+        <f>ABS((D40*E40)-L40)</f>
+        <v>500</v>
+      </c>
+      <c r="N40" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B40, $C$2:$C$776, C40, $D$2:$D$776, D40, $E$2:$E$776, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+    </row>
+    <row r="41" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
+        <v>3760</v>
+      </c>
+      <c r="F41" s="4">
+        <v>-4.4472681070000002</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="4">
-        <v>119</v>
-      </c>
-      <c r="F41" s="4">
-        <v>-5.7500396010000001</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="H41" s="5">
-        <v>126.26</v>
+        <v>3935</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
@@ -3177,81 +3348,77 @@
       </c>
       <c r="P41" s="10"/>
     </row>
-    <row r="42" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="3">
-        <v>46258.601388888892</v>
+    <row r="42" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D42" s="4">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E42" s="4">
-        <v>2271</v>
+        <v>401</v>
       </c>
       <c r="F42" s="4">
-        <v>-5.7285180569999996</v>
+        <v>-4.5578959899999996</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H42" s="5">
-        <v>2409</v>
+        <v>420.15</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J42" s="24" t="s">
+      <c r="J42" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="L42" s="18">
-        <v>7113</v>
-      </c>
-      <c r="M42" s="18">
-        <f>ABS((D42*E42)-L42)</f>
-        <v>300</v>
-      </c>
-      <c r="N42" s="10" t="str">
+      <c r="K42" s="17"/>
+      <c r="L42" s="17"/>
+      <c r="M42" s="17"/>
+      <c r="N42" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B42, $C$2:$C$776, C42, $D$2:$D$776, D42, $E$2:$E$776, E42) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="6" t="s">
-        <v>62</v>
+      <c r="P42" s="10"/>
+    </row>
+    <row r="43" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D43" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4">
-        <v>4640</v>
+        <v>1666</v>
       </c>
       <c r="F43" s="4">
-        <v>-5.7274629719999997</v>
+        <v>-4.8543689319999999</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H43" s="5">
-        <v>4921.8999999999996</v>
+        <v>1751</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="41"/>
+      <c r="J43" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
@@ -3259,86 +3426,81 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B43, $C$2:$C$776, C43, $D$2:$D$776, D43, $E$2:$E$776, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="3">
-        <v>46121.375</v>
+    <row r="44" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" s="4">
-        <v>1614</v>
+        <v>6920</v>
       </c>
       <c r="F44" s="4">
-        <v>-5.6691992989999997</v>
+        <v>-5.2054794519999996</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H44" s="5">
-        <v>1711</v>
+        <v>7300</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="L44" s="18">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M44" s="18">
-        <f>ABS((D44*E44)-L44)</f>
-        <v>540</v>
-      </c>
-      <c r="N44" s="10" t="str">
+      <c r="J44" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B44, $C$2:$C$776, C44, $D$2:$D$776, D44, $E$2:$E$776, E44) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="3">
-        <v>46252.635416666664</v>
+    <row r="45" spans="1:16" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D45" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E45" s="4">
-        <v>1440</v>
+        <v>212</v>
       </c>
       <c r="F45" s="4">
-        <v>-5.5737704920000004</v>
+        <v>-5.2852611359999999</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="H45" s="5">
-        <v>1525</v>
+        <v>223.83</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="41"/>
+      <c r="J45" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K45" s="17"/>
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
@@ -3346,9 +3508,8 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B45, $C$2:$C$776, C45, $D$2:$D$776, D45, $E$2:$E$776, E45) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O45" s="25"/>
-    </row>
-    <row r="46" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
@@ -3389,37 +3550,35 @@
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="6" t="s">
-        <v>62</v>
+    <row r="47" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E47" s="4">
-        <v>212</v>
+        <v>1440</v>
       </c>
       <c r="F47" s="4">
-        <v>-5.2852611359999999</v>
+        <v>-5.5737704920000004</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="H47" s="5">
-        <v>223.83</v>
+        <v>1525</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J47" s="41"/>
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
@@ -3427,79 +3586,86 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B47, $C$2:$C$776, C47, $D$2:$D$776, D47, $E$2:$E$776, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="6" t="s">
-        <v>62</v>
+      <c r="O47" s="25"/>
+    </row>
+    <row r="48" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="3">
+        <v>46121.375</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D48" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="4">
-        <v>6920</v>
+        <v>1614</v>
       </c>
       <c r="F48" s="4">
-        <v>-5.2054794519999996</v>
+        <v>-5.6691992989999997</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="H48" s="5">
-        <v>7300</v>
+        <v>1711</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" t="str">
+      <c r="J48" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="L48" s="18">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M48" s="18">
+        <f>ABS((D48*E48)-L48)</f>
+        <v>540</v>
+      </c>
+      <c r="N48" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B48, $C$2:$C$776, C48, $D$2:$D$776, D48, $E$2:$E$776, E48) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3">
-        <v>46252.6875</v>
+    <row r="49" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4">
-        <v>1666</v>
+        <v>4640</v>
       </c>
       <c r="F49" s="4">
-        <v>-4.8543689319999999</v>
+        <v>-5.7274629719999997</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="H49" s="5">
-        <v>1751</v>
+        <v>4921.8999999999996</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J49" s="41"/>
       <c r="K49" s="17"/>
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
@@ -3507,73 +3673,80 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B49, $C$2:$C$776, C49, $D$2:$D$776, D49, $E$2:$E$776, E49) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="6" t="s">
-        <v>62</v>
+    <row r="50" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="3">
+        <v>46258.601388888892</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D50" s="4">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E50" s="4">
-        <v>401</v>
+        <v>2271</v>
       </c>
       <c r="F50" s="4">
-        <v>-4.5578959899999996</v>
+        <v>-5.7285180569999996</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H50" s="5">
-        <v>420.15</v>
+        <v>2409</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="22" t="s">
+      <c r="J50" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" t="str">
+      <c r="K50" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="L50" s="18">
+        <v>7113</v>
+      </c>
+      <c r="M50" s="18">
+        <f>ABS((D50*E50)-L50)</f>
+        <v>300</v>
+      </c>
+      <c r="N50" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B50, $C$2:$C$776, C50, $D$2:$D$776, D50, $E$2:$E$776, E50) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O50"/>
-    </row>
-    <row r="51" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P50"/>
+    </row>
+    <row r="51" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D51" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E51" s="4">
-        <v>3760</v>
+        <v>119</v>
       </c>
       <c r="F51" s="4">
-        <v>-4.4472681070000002</v>
+        <v>-5.7500396010000001</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="H51" s="5">
-        <v>3935</v>
+        <v>126.26</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
@@ -3588,150 +3761,128 @@
       </c>
       <c r="O51"/>
     </row>
-    <row r="52" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3">
-        <v>46268.385416666664</v>
+    <row r="52" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="4">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="E52" s="4">
-        <v>214</v>
+        <v>1277</v>
       </c>
       <c r="F52" s="4">
-        <v>-4.3917258629999996</v>
+        <v>-5.7564575649999998</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H52" s="5">
-        <v>223.83</v>
+        <v>1355</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="24" t="s">
+      <c r="J52" s="41"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$776, B52, $C$2:$C$776, C52, $D$2:$D$776, D52, $E$2:$E$776, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O52"/>
+      <c r="P52"/>
+    </row>
+    <row r="53" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="4">
+        <v>3</v>
+      </c>
+      <c r="E53" s="4">
+        <v>4710</v>
+      </c>
+      <c r="F53" s="4">
+        <v>-6.119194738</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H53" s="5">
+        <v>5017</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="K52" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="L52" s="18">
-        <v>21900</v>
-      </c>
-      <c r="M52" s="18">
-        <f>ABS((D52*E52)-L52)</f>
-        <v>500</v>
-      </c>
-      <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$776, B52, $C$2:$C$776, C52, $D$2:$D$776, D52, $E$2:$E$776, E52) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="20">
-        <v>46255</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="4">
-        <v>25</v>
-      </c>
-      <c r="E53" s="4">
-        <v>336</v>
-      </c>
-      <c r="F53" s="4">
-        <v>-4.2189281640000003</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H53" s="5">
-        <v>350.8</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J53" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K53" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="L53" s="18">
-        <v>8700</v>
-      </c>
-      <c r="M53" s="18">
-        <f>ABS((D53*E53)-L53)</f>
-        <v>300</v>
-      </c>
-      <c r="N53" s="10" t="str">
+      <c r="K53" s="17"/>
+      <c r="L53" s="17"/>
+      <c r="M53" s="17"/>
+      <c r="N53" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B53, $C$2:$C$776, C53, $D$2:$D$776, D53, $E$2:$E$776, E53) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3">
-        <v>46261.375</v>
+    <row r="54" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="4">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E54" s="4">
-        <v>870</v>
+        <v>411</v>
       </c>
       <c r="F54" s="4">
-        <v>-4.1850220260000004</v>
+        <v>-6.3354603459999996</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="H54" s="5">
-        <v>908</v>
+        <v>438.8</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K54" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="L54" s="18">
-        <v>17700</v>
-      </c>
-      <c r="M54" s="18">
-        <f>ABS((D54*E54)-L54)</f>
-        <v>300</v>
-      </c>
-      <c r="N54" s="10" t="str">
+      <c r="J54" s="41"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B54, $C$2:$C$776, C54, $D$2:$D$776, D54, $E$2:$E$776, E54) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P54" s="25"/>
-    </row>
-    <row r="55" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
-        <v>46268.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>32</v>
@@ -3740,13 +3891,13 @@
         <v>10</v>
       </c>
       <c r="D55" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E55" s="4">
-        <v>870.2</v>
+        <v>850</v>
       </c>
       <c r="F55" s="4">
-        <v>-4.1629955949999999</v>
+        <v>-6.3876651979999997</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>85</v>
@@ -3757,50 +3908,43 @@
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="24" t="s">
+      <c r="J55" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="K55" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="L55" s="18">
-        <v>17920</v>
-      </c>
-      <c r="M55" s="18">
-        <f>ABS((D55*E55)-L55)</f>
-        <v>516</v>
-      </c>
-      <c r="N55" s="10" t="str">
+      <c r="K55" s="17"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B55, $C$2:$C$776, C55, $D$2:$D$776, D55, $E$2:$E$776, E55) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-    </row>
-    <row r="56" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P55"/>
+    </row>
+    <row r="56" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
         <v>46252.635416666664</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4">
-        <v>1132</v>
+        <v>1420</v>
       </c>
       <c r="F56" s="4">
-        <v>-4.0677966100000003</v>
+        <v>-6.8852459020000003</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H56" s="5">
-        <v>1180</v>
+        <v>1525</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
@@ -3813,13 +3957,15 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B56, $C$2:$C$776, C56, $D$2:$D$776, D56, $E$2:$E$776, E56) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3">
-        <v>46258.375694444447</v>
+      <c r="O56"/>
+      <c r="P56"/>
+    </row>
+    <row r="57" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
@@ -3828,67 +3974,64 @@
         <v>10</v>
       </c>
       <c r="E57" s="4">
-        <v>1465</v>
+        <v>561</v>
       </c>
       <c r="F57" s="4">
-        <v>-3.9344262300000001</v>
+        <v>-6.9111424540000002</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H57" s="5">
-        <v>1525</v>
+        <v>602.65</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K57" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="L57" s="18">
-        <v>15100</v>
-      </c>
-      <c r="M57" s="18">
-        <f>ABS((D57*E57)-L57)</f>
-        <v>450</v>
-      </c>
-      <c r="N57" s="10" t="str">
+      <c r="J57" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="K57" s="17"/>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17"/>
+      <c r="N57" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B57, $C$2:$C$776, C57, $D$2:$D$776, D57, $E$2:$E$776, E57) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O57"/>
+      <c r="P57"/>
+    </row>
+    <row r="58" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
-        <v>46252.635416666664</v>
+        <v>46252.6875</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D58" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E58" s="4">
-        <v>1302</v>
+        <v>326</v>
       </c>
       <c r="F58" s="4">
-        <v>-3.9114391140000002</v>
+        <v>-7.0695553020000004</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H58" s="5">
-        <v>1355</v>
+        <v>350.8</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="41"/>
+      <c r="J58" s="41" t="s">
+        <v>41</v>
+      </c>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
@@ -3899,30 +4042,30 @@
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3">
-        <v>46252.688194444447</v>
+    <row r="59" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D59" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4">
-        <v>640</v>
+        <v>4560</v>
       </c>
       <c r="F59" s="4">
-        <v>-3.9039039039999999</v>
+        <v>-7.3528515409999997</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="H59" s="5">
-        <v>666</v>
+        <v>4921.8999999999996</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
@@ -3938,119 +4081,119 @@
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="6" t="s">
-        <v>62</v>
+    <row r="60" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="3">
+        <v>46031.4375</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="4">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E60" s="4">
-        <v>862</v>
+        <v>1052</v>
       </c>
       <c r="F60" s="4">
-        <v>-3.9018952059999998</v>
+        <v>-7.3902900660000004</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>52</v>
+        <v>227</v>
       </c>
       <c r="H60" s="5">
-        <v>897</v>
+        <v>1135.95</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="41" t="s">
+      <c r="J60" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" t="str">
+      <c r="M60" s="18">
+        <f>ABS((D60*E60)-L60)</f>
+        <v>3156</v>
+      </c>
+      <c r="N60" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B60, $C$2:$C$776, C60, $D$2:$D$776, D60, $E$2:$E$776, E60) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O60"/>
-      <c r="P60"/>
-    </row>
-    <row r="61" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="6" t="s">
-        <v>62</v>
+      <c r="P60" s="19"/>
+    </row>
+    <row r="61" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="3">
+        <v>46254.375</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D61" s="4">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="E61" s="4">
-        <v>31.01</v>
+        <v>2230</v>
       </c>
       <c r="F61" s="4">
-        <v>-3.5158680769999999</v>
+        <v>-7.4304690740000003</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H61" s="5">
-        <v>32.14</v>
+        <v>2409</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="41" t="s">
+      <c r="J61" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="K61" s="17"/>
+      <c r="K61" s="17" t="s">
+        <v>148</v>
+      </c>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
-      <c r="N61" t="str">
+      <c r="N61" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B61, $C$2:$C$776, C61, $D$2:$D$776, D61, $E$2:$E$776, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O61" s="34"/>
+      <c r="O61"/>
       <c r="P61"/>
     </row>
-    <row r="62" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="3">
-        <v>46252.6875</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E62" s="4">
-        <v>122</v>
+        <v>1410</v>
       </c>
       <c r="F62" s="4">
-        <v>-3.3739901790000002</v>
+        <v>-7.5409836070000003</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H62" s="5">
-        <v>126.26</v>
+        <v>1525</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="42" t="s">
-        <v>41</v>
-      </c>
+      <c r="J62" s="41"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
@@ -4058,13 +4201,15 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B62, $C$2:$C$776, C62, $D$2:$D$776, D62, $E$2:$E$776, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3">
-        <v>46252.635416666664</v>
+      <c r="O62"/>
+      <c r="P62"/>
+    </row>
+    <row r="63" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
@@ -4073,16 +4218,16 @@
         <v>5</v>
       </c>
       <c r="E63" s="4">
-        <v>1142</v>
+        <v>1614</v>
       </c>
       <c r="F63" s="4">
-        <v>-3.220338983</v>
+        <v>-7.8241005140000004</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="H63" s="5">
-        <v>1180</v>
+        <v>1751</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
@@ -4097,36 +4242,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B63, $C$2:$C$776, C63, $D$2:$D$776, D63, $E$2:$E$776, E63) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O63"/>
+      <c r="P63"/>
+    </row>
+    <row r="64" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D64" s="4">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E64" s="4">
-        <v>3810</v>
+        <v>836</v>
       </c>
       <c r="F64" s="4">
-        <v>-3.1766200759999998</v>
+        <v>-7.9295154190000003</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="H64" s="5">
-        <v>3935</v>
+        <v>908</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="41"/>
+      <c r="J64" s="41" t="s">
+        <v>118</v>
+      </c>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
@@ -4134,31 +4283,33 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B64, $C$2:$C$776, C64, $D$2:$D$776, D64, $E$2:$E$776, E64) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" s="19" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="3">
-        <v>46252.6875</v>
+      <c r="O64"/>
+      <c r="P64"/>
+    </row>
+    <row r="65" spans="1:16" s="19" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E65" s="4">
-        <v>271</v>
+        <v>206</v>
       </c>
       <c r="F65" s="4">
-        <v>-3.0758226039999998</v>
+        <v>-7.9658669529999999</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="H65" s="5">
-        <v>279.60000000000002</v>
+        <v>223.83</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
@@ -4173,40 +4324,38 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B65, $C$2:$C$776, C65, $D$2:$D$776, D65, $E$2:$E$776, E65) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-    </row>
-    <row r="66" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3">
-        <v>46252.6875</v>
+      <c r="O65"/>
+      <c r="P65"/>
+    </row>
+    <row r="66" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D66" s="4">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="E66" s="4">
-        <v>277</v>
+        <v>116</v>
       </c>
       <c r="F66" s="4">
-        <v>-3.0621172350000001</v>
+        <v>-8.1260890230000005</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H66" s="5">
-        <v>285.75</v>
+        <v>126.26</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J66" s="41"/>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
@@ -4215,38 +4364,37 @@
         <v>Unique</v>
       </c>
       <c r="O66"/>
-    </row>
-    <row r="67" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="3">
-        <v>46252.635416666664</v>
+      <c r="P66"/>
+    </row>
+    <row r="67" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E67" s="4">
-        <v>391</v>
+        <v>1751</v>
       </c>
       <c r="F67" s="4">
-        <v>-2.9776674939999999</v>
+        <v>-8.4205020919999995</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="H67" s="5">
-        <v>403</v>
+        <v>1912</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="41" t="s">
-        <v>55</v>
-      </c>
+      <c r="J67" s="41"/>
       <c r="K67" s="17"/>
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
@@ -4254,38 +4402,38 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B67, $C$2:$C$776, C67, $D$2:$D$776, D67, $E$2:$E$776, E67) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O67"/>
+      <c r="P67"/>
+    </row>
+    <row r="68" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D68" s="4">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E68" s="4">
-        <v>201</v>
+        <v>115.25</v>
       </c>
       <c r="F68" s="4">
-        <v>-2.8985507250000002</v>
+        <v>-8.7201013780000007</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="H68" s="5">
-        <v>207</v>
+        <v>126.26</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="42" t="s">
-        <v>41</v>
-      </c>
+      <c r="J68" s="41"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
@@ -4296,163 +4444,156 @@
       <c r="O68"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="3">
-        <v>46121.375</v>
+    <row r="69" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E69" s="4">
-        <v>1664</v>
+        <v>4456</v>
       </c>
       <c r="F69" s="4">
-        <v>-2.7469316190000002</v>
+        <v>-9.465856681</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="H69" s="5">
-        <v>1711</v>
+        <v>4921.8999999999996</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="24" t="s">
+      <c r="J69" s="41"/>
+      <c r="K69" s="17"/>
+      <c r="L69" s="17"/>
+      <c r="M69" s="17"/>
+      <c r="N69" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$776, B69, $C$2:$C$776, C69, $D$2:$D$776, D69, $E$2:$E$776, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O69"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="4">
+        <v>10</v>
+      </c>
+      <c r="E70" s="4">
+        <v>251</v>
+      </c>
+      <c r="F70" s="4">
+        <v>-10.228898429999999</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H70" s="5">
+        <v>279.60000000000002</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" s="41"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
+      <c r="N70" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$776, B70, $C$2:$C$776, C70, $D$2:$D$776, D70, $E$2:$E$776, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O70"/>
+      <c r="P70" s="34"/>
+    </row>
+    <row r="71" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="3">
+        <v>46267.375</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4">
+        <v>20050</v>
+      </c>
+      <c r="F71" s="4">
+        <v>-10.27075408</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H71" s="5">
+        <v>22345</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J71" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="K69" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="L69" s="18">
-        <f>5*1794</f>
-        <v>8970</v>
-      </c>
-      <c r="M69" s="18">
-        <f>ABS((D69*E69)-L69)</f>
-        <v>650</v>
-      </c>
-      <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$776, B69, $C$2:$C$776, C69, $D$2:$D$776, D69, $E$2:$E$776, E69) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O69"/>
-    </row>
-    <row r="70" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="3">
-        <v>46274.375</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="4">
-        <v>15</v>
-      </c>
-      <c r="E70" s="4">
-        <v>1005</v>
-      </c>
-      <c r="F70" s="4">
-        <v>-2.7199690250000002</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H70" s="5">
-        <v>1033.0999999999999</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J70" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K70" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="L70" s="18">
-        <v>15600</v>
-      </c>
-      <c r="M70" s="18">
-        <f>ABS((D70*E70)-L70)</f>
-        <v>525</v>
-      </c>
-      <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$776, B70, $C$2:$C$776, C70, $D$2:$D$776, D70, $E$2:$E$776, E70) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" s="4">
-        <v>2</v>
-      </c>
-      <c r="E71" s="4">
-        <v>4010</v>
-      </c>
-      <c r="F71" s="4">
-        <v>-2.669902913</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H71" s="5">
-        <v>4120</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J71" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" t="str">
+      <c r="K71" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="L71" s="18">
+        <v>20350</v>
+      </c>
+      <c r="M71" s="18">
+        <f>ABS((D71*E71)-L71)</f>
+        <v>300</v>
+      </c>
+      <c r="N71" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B71, $C$2:$C$776, C71, $D$2:$D$776, D71, $E$2:$E$776, E71) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D72" s="4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E72" s="4">
-        <v>3830</v>
+        <v>4415</v>
       </c>
       <c r="F72" s="4">
-        <v>-2.6683608639999998</v>
+        <v>-10.29886832</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H72" s="5">
-        <v>3935</v>
+        <v>4921.8999999999996</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>8</v>
@@ -4465,31 +4606,33 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B72, $C$2:$C$776, C72, $D$2:$D$776, D72, $E$2:$E$776, E72) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O72"/>
+      <c r="P72"/>
+    </row>
+    <row r="73" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D73" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E73" s="4">
-        <v>13052</v>
+        <v>111</v>
       </c>
       <c r="F73" s="4">
-        <v>-2.6551312650000001</v>
+        <v>-12.086171390000001</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H73" s="5">
-        <v>13408</v>
+        <v>126.26</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
@@ -4505,60 +4648,51 @@
       <c r="O73"/>
       <c r="P73"/>
     </row>
-    <row r="74" spans="1:16" s="26" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="3">
-        <v>46260.375</v>
+    <row r="74" spans="1:16" s="26" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D74" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E74" s="4">
-        <v>2348</v>
+        <v>4410</v>
       </c>
       <c r="F74" s="4">
-        <v>-2.5321710249999998</v>
+        <v>-12.09886386</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H74" s="5">
-        <v>2409</v>
+        <v>5017</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K74" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="L74" s="18">
-        <v>7344</v>
-      </c>
-      <c r="M74" s="18">
-        <f>ABS((D74*E74)-L74)</f>
-        <v>300</v>
-      </c>
+      <c r="J74" s="41"/>
+      <c r="K74" s="17"/>
+      <c r="L74" s="17"/>
+      <c r="M74" s="17"/>
       <c r="N74" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B74, $C$2:$C$776, C74, $D$2:$D$776, D74, $E$2:$E$776, E74) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O74" s="10"/>
-      <c r="P74" s="10"/>
-    </row>
-    <row r="75" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O74"/>
+      <c r="P74"/>
+    </row>
+    <row r="75" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
-        <v>46269.375</v>
+        <v>46252.635416666664</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>10</v>
@@ -4567,108 +4701,109 @@
         <v>2</v>
       </c>
       <c r="E75" s="4">
-        <v>3210</v>
+        <v>2892</v>
       </c>
       <c r="F75" s="4">
-        <v>-2.3692934700000001</v>
+        <v>-12.222660640000001</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H75" s="5">
-        <v>3287.9</v>
+        <v>3294.7</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J75" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K75" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="L75" s="18">
-        <v>6880</v>
-      </c>
-      <c r="M75" s="27">
-        <f>ABS((D75*E75)-L75)</f>
-        <v>460</v>
-      </c>
+      <c r="J75" s="41"/>
+      <c r="K75" s="17"/>
+      <c r="L75" s="17"/>
+      <c r="M75" s="17"/>
       <c r="N75" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B75, $C$2:$C$776, C75, $D$2:$D$776, D75, $E$2:$E$776, E75) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O75"/>
-    </row>
-    <row r="76" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D76" s="4">
-        <v>10</v>
-      </c>
-      <c r="E76" s="4">
-        <v>1132</v>
+      <c r="P75"/>
+    </row>
+    <row r="76" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="29">
+        <v>46255</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="31">
+        <v>1</v>
+      </c>
+      <c r="E76" s="31">
+        <v>19550</v>
       </c>
       <c r="F76" s="4">
-        <v>-2.1776702389999998</v>
+        <v>-12.508391140000001</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H76" s="5">
-        <v>1157.2</v>
+        <v>22345</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J76" s="41"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
-      <c r="M76" s="17"/>
-      <c r="N76" t="str">
+      <c r="J76" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="K76" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L76" s="27">
+        <v>19992</v>
+      </c>
+      <c r="M76" s="27">
+        <f>ABS((D76*E76)-L76)</f>
+        <v>442</v>
+      </c>
+      <c r="N76" s="28" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B76, $C$2:$C$776, C76, $D$2:$D$776, D76, $E$2:$E$776, E76) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O76"/>
       <c r="P76"/>
     </row>
-    <row r="77" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D77" s="4">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E77" s="4">
-        <v>878</v>
+        <v>701</v>
       </c>
       <c r="F77" s="4">
-        <v>-2.1181716829999999</v>
+        <v>-12.609861</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="H77" s="5">
-        <v>897</v>
+        <v>802.15</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J77" s="41" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="K77" s="17"/>
       <c r="L77" s="17"/>
@@ -4677,36 +4812,40 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B77, $C$2:$C$776, C77, $D$2:$D$776, D77, $E$2:$E$776, E77) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O77"/>
+      <c r="P77"/>
+    </row>
+    <row r="78" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D78" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="4">
-        <v>3856</v>
+        <v>4364</v>
       </c>
       <c r="F78" s="4">
-        <v>-2.0076238879999999</v>
+        <v>-13.015746460000001</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="H78" s="5">
-        <v>3935</v>
+        <v>5017</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J78" s="41"/>
+      <c r="J78" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
@@ -4714,40 +4853,38 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B78, $C$2:$C$776, C78, $D$2:$D$776, D78, $E$2:$E$776, E78) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O78" s="19"/>
-      <c r="P78" s="10"/>
-    </row>
-    <row r="79" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="3">
-        <v>46252.6875</v>
+      <c r="O78"/>
+      <c r="P78"/>
+    </row>
+    <row r="79" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D79" s="4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E79" s="4">
-        <v>203.5</v>
+        <v>196</v>
       </c>
       <c r="F79" s="4">
-        <v>-1.690821256</v>
+        <v>-13.27433628</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="H79" s="5">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J79" s="42" t="s">
-        <v>55</v>
-      </c>
+      <c r="J79" s="41"/>
       <c r="K79" s="17"/>
       <c r="L79" s="17"/>
       <c r="M79" s="17"/>
@@ -4755,39 +4892,38 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B79, $C$2:$C$776, C79, $D$2:$D$776, D79, $E$2:$E$776, E79) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O79"/>
       <c r="P79"/>
     </row>
-    <row r="80" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D80" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E80" s="4">
-        <v>281</v>
+        <v>19052</v>
       </c>
       <c r="F80" s="4">
-        <v>-1.662292213</v>
+        <v>-14.73707765</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H80" s="5">
-        <v>285.75</v>
+        <v>22345</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="41" t="s">
-        <v>41</v>
-      </c>
+      <c r="J80" s="41"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
@@ -4795,79 +4931,72 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B80, $C$2:$C$776, C80, $D$2:$D$776, D80, $E$2:$E$776, E80) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P80" s="26"/>
-    </row>
-    <row r="81" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="3">
-        <v>46265.466666666667</v>
+      <c r="O80"/>
+      <c r="P80"/>
+    </row>
+    <row r="81" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D81" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E81" s="4">
-        <v>1503</v>
+        <v>2752</v>
       </c>
       <c r="F81" s="4">
-        <v>-1.4426229509999999</v>
+        <v>-16.47190943</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" s="5">
-        <v>1525</v>
+        <v>3294.7</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J81" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="K81" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="L81" s="18">
-        <v>15050</v>
-      </c>
-      <c r="M81" s="18">
-        <f>ABS((D81*E81)-L81)</f>
-        <v>20</v>
-      </c>
+      <c r="J81" s="41"/>
+      <c r="K81" s="17"/>
+      <c r="L81" s="17"/>
+      <c r="M81" s="17"/>
       <c r="N81" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B81, $C$2:$C$776, C81, $D$2:$D$776, D81, $E$2:$E$776, E81) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P81" s="25"/>
-    </row>
-    <row r="82" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O81"/>
+      <c r="P81"/>
+    </row>
+    <row r="82" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D82" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E82" s="4">
-        <v>3888</v>
+        <v>18552</v>
       </c>
       <c r="F82" s="4">
-        <v>-1.1944091489999999</v>
+        <v>-16.9747147</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="H82" s="5">
-        <v>3935</v>
+        <v>22345</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>8</v>
@@ -4880,177 +5009,155 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B82, $C$2:$C$776, C82, $D$2:$D$776, D82, $E$2:$E$776, E82) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O82" s="26"/>
-    </row>
-    <row r="83" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="3">
-        <v>46261.375</v>
+      <c r="O82"/>
+      <c r="P82"/>
+    </row>
+    <row r="83" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D83" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E83" s="4">
-        <v>205</v>
+        <v>4164</v>
       </c>
       <c r="F83" s="4">
-        <v>-0.96618357489999995</v>
+        <v>-17.00219255</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H83" s="5">
-        <v>207</v>
+        <v>5017</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K83" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="L83" s="18">
-        <v>10550</v>
-      </c>
-      <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
-        <v>300</v>
-      </c>
-      <c r="N83" s="10" t="str">
+      <c r="J83" s="41"/>
+      <c r="K83" s="17"/>
+      <c r="L83" s="17"/>
+      <c r="M83" s="17"/>
+      <c r="N83" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B83, $C$2:$C$776, C83, $D$2:$D$776, D83, $E$2:$E$776, E83) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O83"/>
+      <c r="P83"/>
+    </row>
+    <row r="84" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
-        <v>46275.457662037035</v>
+        <v>46252.688194444447</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D84" s="4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="E84" s="4">
-        <v>222</v>
+        <v>136.15</v>
       </c>
       <c r="F84" s="4">
-        <v>-0.81758477419999998</v>
+        <v>-17.424793789999999</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="H84" s="5">
-        <v>223.83</v>
+        <v>164.88</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J84" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="K84" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="L84" s="18">
-        <v>56375</v>
-      </c>
-      <c r="M84" s="18">
-        <f>ABS((D84*E84)-L84)</f>
-        <v>34175</v>
-      </c>
-      <c r="N84" s="10" t="str">
+      <c r="J84" s="41"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="17"/>
+      <c r="N84" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B84, $C$2:$C$776, C84, $D$2:$D$776, D84, $E$2:$E$776, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="3">
-        <v>46269.375</v>
+      <c r="O84"/>
+      <c r="P84"/>
+    </row>
+    <row r="85" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D85" s="4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E85" s="4">
-        <v>348</v>
+        <v>18052</v>
       </c>
       <c r="F85" s="4">
-        <v>-0.79817559859999998</v>
+        <v>-19.212351760000001</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H85" s="5">
-        <v>350.8</v>
+        <v>22345</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J85" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="K85" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="L85" s="18">
-        <v>9000</v>
-      </c>
-      <c r="M85" s="27">
-        <f>ABS((D85*E85)-L85)</f>
-        <v>300</v>
-      </c>
+      <c r="J85" s="41"/>
+      <c r="K85" s="17"/>
+      <c r="L85" s="17"/>
+      <c r="M85" s="17"/>
       <c r="N85" t="str">
         <f>IF(COUNTIFS( $B$2:$B$776, B85, $C$2:$C$776, C85, $D$2:$D$776, D85, $E$2:$E$776, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="3">
-        <v>46252.645138888889</v>
+      <c r="O85"/>
+      <c r="P85"/>
+    </row>
+    <row r="86" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D86" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E86" s="4">
-        <v>401</v>
+        <v>2660</v>
       </c>
       <c r="F86" s="4">
-        <v>-0.49627791560000001</v>
+        <v>-19.26427292</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="H86" s="5">
-        <v>403</v>
+        <v>3294.7</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J86" s="43" t="s">
-        <v>118</v>
-      </c>
+      <c r="J86" s="41"/>
       <c r="K86" s="17"/>
       <c r="L86" s="17"/>
       <c r="M86" s="17"/>
@@ -5058,31 +5165,33 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B86, $C$2:$C$776, C86, $D$2:$D$776, D86, $E$2:$E$776, E86) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O86"/>
+      <c r="P86"/>
+    </row>
+    <row r="87" spans="1:16" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D87" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E87" s="4">
-        <v>2370</v>
+        <v>4014</v>
       </c>
       <c r="F87" s="4">
-        <v>-0.2105263158</v>
+        <v>-19.992027109999999</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H87" s="5">
-        <v>2375</v>
+        <v>5017</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>8</v>
@@ -5095,31 +5204,33 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B87, $C$2:$C$776, C87, $D$2:$D$776, D87, $E$2:$E$776, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O87"/>
+      <c r="P87"/>
+    </row>
+    <row r="88" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D88" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E88" s="4">
-        <v>2435</v>
+        <v>660</v>
       </c>
       <c r="F88" s="4">
-        <v>-0.1230516817</v>
+        <v>-20.390808759999999</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="H88" s="5">
-        <v>2438</v>
+        <v>829.05</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>8</v>
@@ -5132,13 +5243,15 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B88, $C$2:$C$776, C88, $D$2:$D$776, D88, $E$2:$E$776, E88) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" s="25" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="3">
-        <v>46252.635416666664</v>
+      <c r="O88"/>
+      <c r="P88"/>
+    </row>
+    <row r="89" spans="1:16" s="25" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>10</v>
@@ -5147,21 +5260,23 @@
         <v>1</v>
       </c>
       <c r="E89" s="4">
-        <v>13552</v>
+        <v>3914</v>
       </c>
       <c r="F89" s="4">
-        <v>1.0739856800000001</v>
+        <v>-21.985250149999999</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H89" s="5">
-        <v>13408</v>
+        <v>5017</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="41"/>
+      <c r="J89" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
@@ -5169,10 +5284,10 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B89, $C$2:$C$776, C89, $D$2:$D$776, D89, $E$2:$E$776, E89) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O89" s="10"/>
-      <c r="P89" s="10"/>
-    </row>
-    <row r="90" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O89"/>
+      <c r="P89"/>
+    </row>
+    <row r="90" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
         <v>46304.375</v>
       </c>
@@ -5218,30 +5333,30 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="91" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:16" s="35" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D91" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E91" s="4">
-        <v>2470</v>
+        <v>2560</v>
       </c>
       <c r="F91" s="4">
-        <v>1.3125512720000001</v>
+        <v>-22.299450629999999</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H91" s="5">
-        <v>2438</v>
+        <v>3294.7</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>8</v>
@@ -5254,10 +5369,10 @@
         <f>IF(COUNTIFS( $B$2:$B$776, B91, $C$2:$C$776, C91, $D$2:$D$776, D91, $E$2:$E$776, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O91" s="10"/>
-      <c r="P91" s="25"/>
-    </row>
-    <row r="92" spans="1:16" s="35" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O91"/>
+      <c r="P91"/>
+    </row>
+    <row r="92" spans="1:16" s="35" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="36">
         <v>46267.375</v>
       </c>
@@ -5307,7 +5422,7 @@
       </c>
       <c r="P92" s="10"/>
     </row>
-    <row r="93" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="36">
         <v>46267.375</v>
       </c>
@@ -5356,7 +5471,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>46304.375</v>
       </c>
@@ -5402,7 +5517,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="54">
         <v>46273.375</v>
       </c>
@@ -5450,7 +5565,7 @@
       <c r="O95" s="35"/>
       <c r="P95" s="35"/>
     </row>
-    <row r="96" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="36">
         <v>46274.375</v>
       </c>
@@ -5498,7 +5613,7 @@
       <c r="O96" s="35"/>
       <c r="P96" s="35"/>
     </row>
-    <row r="97" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>46304.375</v>
       </c>
@@ -5546,7 +5661,7 @@
       <c r="O97" s="10"/>
       <c r="P97" s="10"/>
     </row>
-    <row r="98" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46274.375</v>
       </c>
@@ -5594,7 +5709,7 @@
       <c r="O98" s="10"/>
       <c r="P98" s="10"/>
     </row>
-    <row r="99" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46275.375636574077</v>
       </c>
@@ -5642,7 +5757,7 @@
       <c r="O99" s="10"/>
       <c r="P99" s="10"/>
     </row>
-    <row r="100" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -5691,7 +5806,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="101" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46267.375</v>
       </c>
@@ -5741,7 +5856,7 @@
       </c>
       <c r="P101" s="10"/>
     </row>
-    <row r="102" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="36">
         <v>46262.375</v>
       </c>
@@ -5790,7 +5905,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -5840,7 +5955,7 @@
       </c>
       <c r="P103" s="10"/>
     </row>
-    <row r="104" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="11">
         <v>46243.375</v>
       </c>
@@ -5887,7 +6002,7 @@
       </c>
       <c r="O104" s="10"/>
     </row>
-    <row r="105" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -5933,7 +6048,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="106" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>46273.375</v>
       </c>
@@ -5983,7 +6098,7 @@
       </c>
       <c r="P106" s="10"/>
     </row>
-    <row r="107" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -6030,7 +6145,7 @@
       </c>
       <c r="O107"/>
     </row>
-    <row r="108" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46275.508009259262</v>
       </c>
@@ -6078,7 +6193,7 @@
       <c r="O108" s="10"/>
       <c r="P108" s="10"/>
     </row>
-    <row r="109" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="61">
         <v>46265.375694444447</v>
       </c>
@@ -6128,7 +6243,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6162,7 +6277,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="111" spans="1:16" s="19" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:16" s="19" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>46274.375</v>
       </c>
@@ -6210,7 +6325,7 @@
       <c r="O111" s="10"/>
       <c r="P111" s="10"/>
     </row>
-    <row r="112" spans="1:16" s="26" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:16" s="26" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46275.375625000001</v>
       </c>
@@ -6258,7 +6373,7 @@
       <c r="O112" s="10"/>
       <c r="P112" s="10"/>
     </row>
-    <row r="113" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -6307,7 +6422,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>46261.375</v>
       </c>
@@ -6354,7 +6469,7 @@
       </c>
       <c r="O114"/>
     </row>
-    <row r="115" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6395,7 +6510,7 @@
       </c>
       <c r="P115"/>
     </row>
-    <row r="116" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46274.375</v>
       </c>
@@ -6441,7 +6556,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="8" t="s">
         <v>62</v>
       </c>
@@ -6475,7 +6590,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>46266.375</v>
       </c>
@@ -6522,7 +6637,7 @@
       </c>
       <c r="P118" s="35"/>
     </row>
-    <row r="119" spans="1:16" s="25" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:16" s="25" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="11">
         <v>46273.375</v>
       </c>
@@ -6570,7 +6685,7 @@
       <c r="O119" s="10"/>
       <c r="P119" s="10"/>
     </row>
-    <row r="120" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -6619,7 +6734,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="121" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>46262.375</v>
       </c>
@@ -6665,7 +6780,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="122" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="11">
         <v>46243.375</v>
       </c>
@@ -6712,7 +6827,7 @@
       </c>
       <c r="P122" s="26"/>
     </row>
-    <row r="123" spans="1:16" s="26" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:16" s="26" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -6755,7 +6870,7 @@
       </c>
       <c r="P123"/>
     </row>
-    <row r="124" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="36">
         <v>46260.556944444441</v>
       </c>
@@ -6801,7 +6916,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="36">
         <v>46261.375</v>
       </c>
@@ -6847,7 +6962,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="126" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="36">
         <v>46269.542361111111</v>
       </c>
@@ -6896,7 +7011,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="127" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="36">
         <v>46272.530555555553</v>
       </c>
@@ -6945,7 +7060,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="128" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -6980,7 +7095,7 @@
       </c>
       <c r="O128" s="25"/>
     </row>
-    <row r="129" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3">
         <v>46275.508009259262</v>
       </c>
@@ -7026,7 +7141,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3">
         <v>46274.375</v>
       </c>
@@ -7072,7 +7187,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="131" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3">
         <v>46266.375</v>
       </c>
@@ -7121,7 +7236,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -7170,7 +7285,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3">
         <v>46275.375625000001</v>
       </c>
@@ -7216,7 +7331,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="134" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3">
         <v>46262.375</v>
       </c>
@@ -7263,7 +7378,7 @@
       </c>
       <c r="O134" s="35"/>
     </row>
-    <row r="135" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46267.375</v>
       </c>
@@ -7310,7 +7425,7 @@
       </c>
       <c r="P135" s="19"/>
     </row>
-    <row r="136" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="11">
         <v>46252.6875</v>
       </c>
@@ -7349,7 +7464,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46267.425694444442</v>
       </c>
@@ -7398,7 +7513,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="138" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7439,7 +7554,7 @@
       <c r="O138" s="10"/>
       <c r="P138" s="10"/>
     </row>
-    <row r="139" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -7489,7 +7604,7 @@
       </c>
       <c r="P139"/>
     </row>
-    <row r="140" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7538,7 +7653,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="3">
         <v>46268.375</v>
       </c>
@@ -7584,7 +7699,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -7632,7 +7747,7 @@
       <c r="O142"/>
       <c r="P142"/>
     </row>
-    <row r="143" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7678,7 +7793,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46261.375</v>
       </c>
@@ -7724,7 +7839,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="39">
         <v>46255</v>
       </c>
@@ -7771,7 +7886,7 @@
       </c>
       <c r="P145" s="35"/>
     </row>
-    <row r="146" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="36">
         <v>46261.385416666664</v>
       </c>
@@ -7817,7 +7932,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="147" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="3">
         <v>46267.375</v>
       </c>
@@ -7864,7 +7979,7 @@
       </c>
       <c r="P147" s="26"/>
     </row>
-    <row r="148" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46267.375</v>
       </c>
@@ -7910,7 +8025,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="11">
         <v>46243.375</v>
       </c>
@@ -7959,7 +8074,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="8" t="s">
         <v>62</v>
       </c>
@@ -7995,7 +8110,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="56">
         <v>46273.385416666664</v>
       </c>
@@ -8045,7 +8160,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="152" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8094,7 +8209,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="153" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="8" t="s">
         <v>62</v>
       </c>
@@ -8128,7 +8243,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46275.508009259262</v>
       </c>
@@ -8174,7 +8289,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="155" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -8224,7 +8339,7 @@
       </c>
       <c r="P155" s="35"/>
     </row>
-    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8270,7 +8385,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -8316,7 +8431,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="36">
         <v>46266.375694444447</v>
       </c>
@@ -8364,7 +8479,7 @@
       <c r="O158" s="10"/>
       <c r="P158" s="10"/>
     </row>
-    <row r="159" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3">
         <v>46267.424305555556</v>
       </c>
@@ -8410,7 +8525,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="160" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8459,7 +8574,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="161" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -8505,7 +8620,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46269.643055555556</v>
       </c>
@@ -8551,7 +8666,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="163" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -8599,7 +8714,7 @@
       <c r="O163" s="10"/>
       <c r="P163" s="10"/>
     </row>
-    <row r="164" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8634,7 +8749,7 @@
       </c>
       <c r="O164" s="35"/>
     </row>
-    <row r="165" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="36">
         <v>46267.461111111108</v>
       </c>
@@ -8681,7 +8796,7 @@
       </c>
       <c r="O165" s="26"/>
     </row>
-    <row r="166" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="36">
         <v>46267.38958333333</v>
       </c>
@@ -8727,7 +8842,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="167" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="3">
         <v>46266.375</v>
       </c>
@@ -8773,7 +8888,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="168" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="8" t="s">
         <v>62</v>
       </c>
@@ -8809,7 +8924,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8855,7 +8970,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="170" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3">
         <v>46262.375</v>
       </c>
@@ -8901,7 +9016,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -8947,7 +9062,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="172" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="3">
         <v>46267.375</v>
       </c>
@@ -8993,7 +9108,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="11">
         <v>46252.6875</v>
       </c>
@@ -9029,7 +9144,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="174" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -9072,7 +9187,7 @@
       <c r="O174" s="10"/>
       <c r="P174" s="10"/>
     </row>
-    <row r="175" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3">
         <v>46274.375</v>
       </c>
@@ -9118,7 +9233,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="176" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -9167,7 +9282,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -9213,7 +9328,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -9259,7 +9374,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -9308,7 +9423,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="8" t="s">
         <v>62</v>
       </c>
@@ -9342,7 +9457,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="181" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9381,7 +9496,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="182" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -9428,7 +9543,7 @@
       </c>
       <c r="P182" s="35"/>
     </row>
-    <row r="183" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -9474,7 +9589,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="8" t="s">
         <v>62</v>
       </c>
@@ -9508,7 +9623,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="3">
         <v>46262.375</v>
       </c>
@@ -9554,7 +9669,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46265.486111111109</v>
       </c>
@@ -9600,7 +9715,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="187" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="11">
         <v>46252.6875</v>
       </c>
@@ -9636,7 +9751,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="188" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9670,7 +9785,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="189" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -9718,7 +9833,7 @@
       <c r="O189" s="10"/>
       <c r="P189" s="10"/>
     </row>
-    <row r="190" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="57" t="s">
         <v>62</v>
       </c>
@@ -9761,7 +9876,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46272.451388888891</v>
       </c>
@@ -9807,7 +9922,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3">
         <v>46272.390972222223</v>
       </c>
@@ -9853,7 +9968,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="36">
         <v>46265.375694444447</v>
       </c>
@@ -9900,7 +10015,7 @@
       </c>
       <c r="O193" s="35"/>
     </row>
-    <row r="194" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="54">
         <v>46243.505555555559</v>
       </c>
@@ -9947,7 +10062,7 @@
       </c>
       <c r="O194" s="35"/>
     </row>
-    <row r="195" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3">
         <v>46266.375</v>
       </c>
@@ -9996,7 +10111,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="196" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10042,7 +10157,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="197" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="8" t="s">
         <v>62</v>
       </c>
@@ -10076,7 +10191,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10122,7 +10237,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10158,7 +10273,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10192,7 +10307,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="11">
         <v>46252.6875</v>
       </c>
@@ -10226,7 +10341,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -10261,7 +10376,7 @@
       </c>
       <c r="P202" s="35"/>
     </row>
-    <row r="203" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -10309,7 +10424,7 @@
       <c r="O203" s="10"/>
       <c r="P203" s="10"/>
     </row>
-    <row r="204" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="3">
         <v>46259.375</v>
       </c>
@@ -10356,7 +10471,7 @@
       </c>
       <c r="P204" s="35"/>
     </row>
-    <row r="205" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="3">
         <v>46261.375</v>
       </c>
@@ -10403,7 +10518,7 @@
       </c>
       <c r="O205" s="35"/>
     </row>
-    <row r="206" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="8" t="s">
         <v>62</v>
       </c>
@@ -10439,7 +10554,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="36">
         <v>46258.443749999999</v>
       </c>
@@ -10487,7 +10602,7 @@
       <c r="O207" s="35"/>
       <c r="P207" s="35"/>
     </row>
-    <row r="208" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="54">
         <v>46253.4</v>
       </c>
@@ -10528,7 +10643,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="209" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -10578,7 +10693,7 @@
       </c>
       <c r="P209" s="10"/>
     </row>
-    <row r="210" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="8" t="s">
         <v>62</v>
       </c>
@@ -10614,7 +10729,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="211" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="8" t="s">
         <v>62</v>
       </c>
@@ -10650,7 +10765,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3">
         <v>46260.375</v>
       </c>
@@ -10696,7 +10811,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="8" t="s">
         <v>62</v>
       </c>
@@ -10730,7 +10845,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="214" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="8" t="s">
         <v>62</v>
       </c>
@@ -10766,7 +10881,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="215" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="3">
         <v>46261.375</v>
       </c>
@@ -10812,7 +10927,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46269.375</v>
       </c>
@@ -10858,7 +10973,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="217" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="8" t="s">
         <v>62</v>
       </c>
@@ -10892,7 +11007,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="218" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -10939,7 +11054,7 @@
       </c>
       <c r="P218" s="35"/>
     </row>
-    <row r="219" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="8" t="s">
         <v>62</v>
       </c>
@@ -10975,7 +11090,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="220" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="3">
         <v>46268.375</v>
       </c>
@@ -11021,7 +11136,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="3">
         <v>46261.375</v>
       </c>
@@ -11067,7 +11182,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="3">
         <v>46262.375</v>
       </c>
@@ -11114,7 +11229,7 @@
       </c>
       <c r="P222" s="35"/>
     </row>
-    <row r="223" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="8" t="s">
         <v>62</v>
       </c>
@@ -11150,7 +11265,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -11186,7 +11301,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="3">
         <v>46259.375</v>
       </c>
@@ -11233,7 +11348,7 @@
       </c>
       <c r="O225" s="35"/>
     </row>
-    <row r="226" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="8" t="s">
         <v>62</v>
       </c>
@@ -11270,7 +11385,7 @@
       </c>
       <c r="O226" s="35"/>
     </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="11">
         <v>46253.375</v>
       </c>
@@ -11309,7 +11424,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="9" t="s">
         <v>62</v>
       </c>
@@ -11343,7 +11458,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="229" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="8" t="s">
         <v>62</v>
       </c>
@@ -11377,7 +11492,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="230" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="11">
         <v>46253.375</v>
       </c>
@@ -11416,7 +11531,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="231" spans="1:16" s="35" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:16" s="35" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="11">
         <v>46252.6875</v>
       </c>
@@ -11457,7 +11572,7 @@
       <c r="O231" s="10"/>
       <c r="P231" s="10"/>
     </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -11503,7 +11618,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="233" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="8" t="s">
         <v>62</v>
       </c>
@@ -11539,7 +11654,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="234" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="3">
         <v>46262.375</v>
       </c>
@@ -11585,7 +11700,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="8" t="s">
         <v>62</v>
       </c>
@@ -11621,7 +11736,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="236" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -11662,7 +11777,7 @@
       <c r="O236" s="10"/>
       <c r="P236" s="10"/>
     </row>
-    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="8" t="s">
         <v>62</v>
       </c>
@@ -11699,7 +11814,7 @@
       </c>
       <c r="P237" s="35"/>
     </row>
-    <row r="238" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11734,7 +11849,7 @@
       </c>
       <c r="O238" s="35"/>
     </row>
-    <row r="239" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="8" t="s">
         <v>62</v>
       </c>
@@ -11768,7 +11883,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="240" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="8" t="s">
         <v>62</v>
       </c>
@@ -11804,7 +11919,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="241" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="8" t="s">
         <v>62</v>
       </c>
@@ -11840,7 +11955,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="242" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -11886,7 +12001,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="243" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="3">
         <v>46266.375</v>
       </c>
@@ -11932,7 +12047,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="244" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -11966,7 +12081,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="245" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12005,7 +12120,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="246" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="8" t="s">
         <v>62</v>
       </c>
@@ -12039,7 +12154,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="247" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="20">
         <v>46255</v>
       </c>
@@ -12085,7 +12200,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="248" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="8" t="s">
         <v>62</v>
       </c>
@@ -12119,7 +12234,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="249" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="3">
         <v>46260.375</v>
       </c>
@@ -12166,7 +12281,7 @@
       </c>
       <c r="P249" s="35"/>
     </row>
-    <row r="250" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="3">
         <v>46260.375</v>
       </c>
@@ -12212,7 +12327,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="251" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>62</v>
       </c>
@@ -12246,7 +12361,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="252" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -12282,7 +12397,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="253" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="8" t="s">
         <v>62</v>
       </c>
@@ -12316,7 +12431,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="254" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -12362,7 +12477,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="255" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -12410,7 +12525,7 @@
       <c r="O255" s="10"/>
       <c r="P255" s="10"/>
     </row>
-    <row r="256" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="11">
         <v>46252.6875</v>
       </c>
@@ -12447,7 +12562,7 @@
       </c>
       <c r="O256" s="35"/>
     </row>
-    <row r="257" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="8" t="s">
         <v>62</v>
       </c>
@@ -12481,7 +12596,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="258" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="8" t="s">
         <v>62</v>
       </c>
@@ -12517,7 +12632,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="259" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
         <v>62</v>
       </c>
@@ -12551,7 +12666,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="260" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="8" t="s">
         <v>62</v>
       </c>
@@ -12585,7 +12700,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="261" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="8" t="s">
         <v>62</v>
       </c>
@@ -12619,7 +12734,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="262" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -12666,7 +12781,7 @@
       </c>
       <c r="P262" s="35"/>
     </row>
-    <row r="263" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -12712,7 +12827,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="264" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="8" t="s">
         <v>62</v>
       </c>
@@ -12753,7 +12868,7 @@
       <c r="O264" s="10"/>
       <c r="P264" s="10"/>
     </row>
-    <row r="265" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="8" t="s">
         <v>62</v>
       </c>
@@ -12788,7 +12903,7 @@
       </c>
       <c r="P265" s="35"/>
     </row>
-    <row r="266" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -12834,7 +12949,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="8" t="s">
         <v>62</v>
       </c>
@@ -12868,7 +12983,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="268" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="8" t="s">
         <v>62</v>
       </c>
@@ -12904,7 +13019,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -12938,7 +13053,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="270" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="8" t="s">
         <v>62</v>
       </c>
@@ -12975,7 +13090,7 @@
       </c>
       <c r="O270" s="35"/>
     </row>
-    <row r="271" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A271" s="8" t="s">
         <v>62</v>
       </c>
@@ -13010,7 +13125,7 @@
       </c>
       <c r="O271" s="35"/>
     </row>
-    <row r="272" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="8" t="s">
         <v>62</v>
       </c>
@@ -13044,7 +13159,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="273" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="8" t="s">
         <v>62</v>
       </c>
@@ -13078,7 +13193,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="274" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A274" s="8" t="s">
         <v>62</v>
       </c>
@@ -13112,7 +13227,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="275" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="8" t="s">
         <v>62</v>
       </c>
@@ -13146,7 +13261,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="276" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="8" t="s">
         <v>62</v>
       </c>
@@ -13180,7 +13295,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="277" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="11">
         <v>46252.6875</v>
       </c>
@@ -13216,7 +13331,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="8" t="s">
         <v>62</v>
       </c>
@@ -13252,7 +13367,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="279" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="8" t="s">
         <v>62</v>
       </c>
@@ -13286,7 +13401,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="280" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="8" t="s">
         <v>62</v>
       </c>
@@ -13321,7 +13436,7 @@
       </c>
       <c r="P280" s="35"/>
     </row>
-    <row r="281" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="8" t="s">
         <v>62</v>
       </c>
@@ -13357,7 +13472,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="282" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13393,7 +13508,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="283" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="8" t="s">
         <v>62</v>
       </c>
@@ -13427,7 +13542,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="284" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -13473,7 +13588,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="285" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="8" t="s">
         <v>62</v>
       </c>
@@ -13507,7 +13622,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="286" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="8" t="s">
         <v>62</v>
       </c>
@@ -13541,7 +13656,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="287" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="11">
         <v>46251.506249999999</v>
       </c>
@@ -13576,7 +13691,7 @@
       </c>
       <c r="O287" s="35"/>
     </row>
-    <row r="288" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="8" t="s">
         <v>62</v>
       </c>
@@ -13614,11 +13729,14 @@
   <autoFilter ref="A1:P288" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="S"/>
+        <filter val="B"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P288">
-      <sortCondition ref="F1"/>
+    <filterColumn colId="14">
+      <filters blank="1"/>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P91">
+      <sortCondition descending="1" ref="F1:F288"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -18125,7 +18243,7 @@
       </c>
       <c r="O99" s="10"/>
     </row>
-    <row r="100" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46266.375</v>
       </c>
@@ -18175,7 +18293,7 @@
       </c>
       <c r="P100" s="10"/>
     </row>
-    <row r="101" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -18225,7 +18343,7 @@
       </c>
       <c r="P101" s="10"/>
     </row>
-    <row r="102" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -18507,7 +18625,7 @@
       </c>
       <c r="P107" s="10"/>
     </row>
-    <row r="108" spans="1:16" s="35" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" s="35" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -25987,7 +26105,7 @@
   <autoFilter ref="A1:P288" xr:uid="{06718F09-7A1B-4B8F-8A4F-9C5F6D64A28A}">
     <filterColumn colId="1">
       <filters>
-        <filter val="LTEQ"/>
+        <filter val="GRSEEQ"/>
       </filters>
     </filterColumn>
     <filterColumn colId="14">
